--- a/data/trans_orig/P36$cafe-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36$cafe-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según alimentos que desayuna habitualmente (multirrespuesta) en 2007</t>
+          <t>Población según alimentos que desayuna habitualmente (multirrespuesta) en 2007 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>935853</t>
+          <t>937117</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>969811</t>
+          <t>969262</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1208957</t>
+          <t>1208892</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1245822</t>
+          <t>1245283</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2160914</t>
+          <t>2159286</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2209713</t>
+          <t>2207589</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,31%</t>
         </is>
       </c>
     </row>
@@ -830,112 +830,112 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Pan, tostadas, galletas, cereales, bolleria, ...</t>
+          <t>Fruta y/o zumo</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>786069</t>
+          <t>63842</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>757454</t>
+          <t>49788</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>811243</t>
+          <t>81110</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1051349</t>
+          <t>92116</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1024579</t>
+          <t>74834</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1079705</t>
+          <t>110494</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>1823</t>
+          <t>155</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1837418</t>
+          <t>155958</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1796589</t>
+          <t>132649</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1874661</t>
+          <t>181229</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -943,112 +943,112 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Fruta y/o zumo</t>
+          <t>Alimentos como huevos, queso, jamón, ...</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>63842</t>
+          <t>22379</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>49084</t>
+          <t>13584</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>79683</t>
+          <t>33651</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>92116</t>
+          <t>15613</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>74030</t>
+          <t>9354</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>113000</t>
+          <t>25058</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>36</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>155958</t>
+          <t>37992</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>132416</t>
+          <t>26587</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>184274</t>
+          <t>51993</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -1056,112 +1056,112 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Alimentos como huevos, queso, jamón, ...</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22379</t>
+          <t>26668</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14094</t>
+          <t>17703</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33736</t>
+          <t>39289</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15613</t>
+          <t>15076</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9073</t>
+          <t>8768</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26587</t>
+          <t>25200</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>40</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>37992</t>
+          <t>41744</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27235</t>
+          <t>30247</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52250</t>
+          <t>55864</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19039</t>
+          <t>19378</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>40709</t>
+          <t>40175</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>21850</t>
+          <t>21690</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>42819</t>
+          <t>43271</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>46780</t>
+          <t>46292</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>77802</t>
+          <t>77242</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -1282,112 +1282,112 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Pan, tostadas, galletas, cereales, bolleria, ...</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>792</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26668</t>
+          <t>786069</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18437</t>
+          <t>756456</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>38849</t>
+          <t>813061</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15076</t>
+          <t>1051349</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8220</t>
+          <t>1021960</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24517</t>
+          <t>1079089</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1823</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>41744</t>
+          <t>1837418</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>29803</t>
+          <t>1794491</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>55647</t>
+          <t>1875983</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>80,14%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1515109</t>
+          <t>1513540</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1562601</t>
+          <t>1563711</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1400593</t>
+          <t>1401031</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1448199</t>
+          <t>1447547</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2928490</t>
+          <t>2928143</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2999124</t>
+          <t>2996431</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,41%</t>
         </is>
       </c>
     </row>
@@ -1512,112 +1512,112 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Pan, tostadas, galletas, cereales, bolleria, ...</t>
+          <t>Fruta y/o zumo</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>123</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1296831</t>
+          <t>132454</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1261607</t>
+          <t>112230</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1331799</t>
+          <t>158636</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1204</t>
+          <t>188</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1230158</t>
+          <t>193335</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1199886</t>
+          <t>169040</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1264637</t>
+          <t>220069</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>2468</t>
+          <t>311</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2526989</t>
+          <t>325789</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2481082</t>
+          <t>291855</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2572077</t>
+          <t>360430</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>11,0%</t>
         </is>
       </c>
     </row>
@@ -1625,112 +1625,112 @@
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Fruta y/o zumo</t>
+          <t>Alimentos como huevos, queso, jamón, ...</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>73</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>132454</t>
+          <t>77595</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>110137</t>
+          <t>61341</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>157250</t>
+          <t>97172</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>193335</t>
+          <t>47063</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>167542</t>
+          <t>35112</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>219969</t>
+          <t>62535</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>118</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>325789</t>
+          <t>124657</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>291186</t>
+          <t>102310</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>359871</t>
+          <t>148443</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -1738,112 +1738,112 @@
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Alimentos como huevos, queso, jamón, ...</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>77595</t>
+          <t>33928</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61451</t>
+          <t>23731</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>97576</t>
+          <t>45124</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>47063</t>
+          <t>30590</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34606</t>
+          <t>21118</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62792</t>
+          <t>42055</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>66</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>124657</t>
+          <t>64518</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>104696</t>
+          <t>50228</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>151014</t>
+          <t>81451</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15597</t>
+          <t>15003</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36245</t>
+          <t>35505</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13329</t>
+          <t>13287</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31396</t>
+          <t>31598</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>33252</t>
+          <t>33038</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>59619</t>
+          <t>60997</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -1964,112 +1964,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Pan, tostadas, galletas, cereales, bolleria, ...</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>33928</t>
+          <t>1296831</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24055</t>
+          <t>1260857</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>46138</t>
+          <t>1331896</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>30590</t>
+          <t>1230158</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20636</t>
+          <t>1196006</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>42077</t>
+          <t>1262123</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>2468</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>64518</t>
+          <t>2526989</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>50681</t>
+          <t>2476859</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>82063</t>
+          <t>2576084</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>78,59%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>482211</t>
+          <t>483607</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>510887</t>
+          <t>510235</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>422858</t>
+          <t>421618</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>446700</t>
+          <t>446049</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>913248</t>
+          <t>913680</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>951138</t>
+          <t>951878</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,77%</t>
         </is>
       </c>
     </row>
@@ -2194,112 +2194,112 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Pan, tostadas, galletas, cereales, bolleria, ...</t>
+          <t>Fruta y/o zumo</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>416877</t>
+          <t>68323</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>396925</t>
+          <t>54085</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>436883</t>
+          <t>88940</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>68</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>355499</t>
+          <t>73837</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>334367</t>
+          <t>58777</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>375543</t>
+          <t>90631</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>131</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>772377</t>
+          <t>142160</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>740927</t>
+          <t>121458</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>798071</t>
+          <t>165267</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>16,11%</t>
         </is>
       </c>
     </row>
@@ -2307,112 +2307,112 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Fruta y/o zumo</t>
+          <t>Alimentos como huevos, queso, jamón, ...</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>68323</t>
+          <t>18018</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>53015</t>
+          <t>10652</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>86605</t>
+          <t>27958</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>73837</t>
+          <t>7983</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>58356</t>
+          <t>3560</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>92592</t>
+          <t>16974</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>142160</t>
+          <t>26001</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>121455</t>
+          <t>16812</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>167738</t>
+          <t>38790</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -2420,42 +2420,42 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Alimentos como huevos, queso, jamón, ...</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>18018</t>
+          <t>6946</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10533</t>
+          <t>2819</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29617</t>
+          <t>13931</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2465,67 +2465,67 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7983</t>
+          <t>7884</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3317</t>
+          <t>3418</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17033</t>
+          <t>15343</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>26001</t>
+          <t>14829</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17628</t>
+          <t>8656</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38840</t>
+          <t>24431</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2689</t>
+          <t>2630</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13702</t>
+          <t>13329</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>975</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8563</t>
+          <t>9038</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5355</t>
+          <t>5179</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19772</t>
+          <t>19134</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -2646,112 +2646,112 @@
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Pan, tostadas, galletas, cereales, bolleria, ...</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>395</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6946</t>
+          <t>416877</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2758</t>
+          <t>396327</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13239</t>
+          <t>436775</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>338</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7884</t>
+          <t>355499</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3138</t>
+          <t>337044</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14834</t>
+          <t>374473</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>733</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>14829</t>
+          <t>772377</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>8611</t>
+          <t>740772</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>25503</t>
+          <t>799019</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>77,87%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2958647</t>
+          <t>2953472</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3022335</t>
+          <t>3020686</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3060053</t>
+          <t>3055452</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3122923</t>
+          <t>3122071</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6039320</t>
+          <t>6033195</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6124212</t>
+          <t>6125749</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,19%</t>
         </is>
       </c>
     </row>
@@ -2876,112 +2876,112 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Pan, tostadas, galletas, cereales, bolleria, ...</t>
+          <t>Fruta y/o zumo</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>250</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2499777</t>
+          <t>264619</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2451660</t>
+          <t>232577</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2546062</t>
+          <t>300228</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2573</t>
+          <t>347</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2637007</t>
+          <t>359288</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2591023</t>
+          <t>321891</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2683720</t>
+          <t>392999</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>597</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5136784</t>
+          <t>623906</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5070013</t>
+          <t>573255</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5205592</t>
+          <t>671909</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>10,11%</t>
         </is>
       </c>
     </row>
@@ -2989,112 +2989,112 @@
       <c r="A24" s="1" t="n"/>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Fruta y/o zumo</t>
+          <t>Alimentos como huevos, queso, jamón, ...</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>110</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>264619</t>
+          <t>117992</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>234573</t>
+          <t>96616</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>300452</t>
+          <t>143034</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>67</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>359288</t>
+          <t>70658</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>326152</t>
+          <t>55733</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>398925</t>
+          <t>89664</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>177</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>623906</t>
+          <t>188650</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>579619</t>
+          <t>161452</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>676510</t>
+          <t>216795</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -3102,112 +3102,112 @@
       <c r="A25" s="1" t="n"/>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Alimentos como huevos, queso, jamón, ...</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>117992</t>
+          <t>67542</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>99597</t>
+          <t>52059</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>142048</t>
+          <t>85648</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>70658</t>
+          <t>53550</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>55194</t>
+          <t>39420</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>89177</t>
+          <t>69792</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>120</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>188650</t>
+          <t>121092</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>162591</t>
+          <t>101491</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>218052</t>
+          <t>145377</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>46143</t>
+          <t>46331</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>76136</t>
+          <t>77733</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,77 +3245,77 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>55531</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>42427</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>71113</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>2,11%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>114886</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>93955</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>138486</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>1,41%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>55531</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>41555</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>70627</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>114886</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>96628</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>138150</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3328,112 +3328,112 @@
       <c r="A27" s="1" t="n"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Pan, tostadas, galletas, cereales, bolleria, ...</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>67542</t>
+          <t>2499777</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>53617</t>
+          <t>2447433</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>86118</t>
+          <t>2549606</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>2573</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>53550</t>
+          <t>2637007</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>40235</t>
+          <t>2586715</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>68593</t>
+          <t>2685599</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>5024</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>121092</t>
+          <t>5136784</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>100811</t>
+          <t>5069578</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>146599</t>
+          <t>5206523</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>78,35%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según alimentos que desayuna habitualmente (multirrespuesta) en 2012</t>
+          <t>Población según alimentos que desayuna habitualmente (multirrespuesta) en 2012 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>882378</t>
+          <t>882054</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>915597</t>
+          <t>915238</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1256652</t>
+          <t>1256719</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1289229</t>
+          <t>1288499</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2149405</t>
+          <t>2148660</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2197341</t>
+          <t>2195213</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,1%</t>
         </is>
       </c>
     </row>
@@ -3789,112 +3789,112 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Pan, tostadas, galletas, cereales, bolleria, ...</t>
+          <t>Fruta y/o zumo</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>774630</t>
+          <t>86935</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>747319</t>
+          <t>67951</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>799574</t>
+          <t>105299</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>124</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1133501</t>
+          <t>133215</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1101706</t>
+          <t>113525</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1160046</t>
+          <t>157483</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>1775</t>
+          <t>203</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1908131</t>
+          <t>220150</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1867520</t>
+          <t>189979</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1942864</t>
+          <t>249970</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>10,83%</t>
         </is>
       </c>
     </row>
@@ -3902,112 +3902,112 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Fruta y/o zumo</t>
+          <t>Alimentos como huevos, queso, jamón, ...</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>86935</t>
+          <t>38671</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>70909</t>
+          <t>28406</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>108374</t>
+          <t>53026</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>133215</t>
+          <t>25403</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>111885</t>
+          <t>16444</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>155402</t>
+          <t>37288</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>60</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>220150</t>
+          <t>64074</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>191939</t>
+          <t>50186</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>252176</t>
+          <t>82481</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -4015,112 +4015,112 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Alimentos como huevos, queso, jamón, ...</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>38671</t>
+          <t>24706</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27569</t>
+          <t>15741</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51602</t>
+          <t>37699</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25403</t>
+          <t>9084</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17019</t>
+          <t>3892</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37662</t>
+          <t>16968</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
           <t>1,27%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>30</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>64074</t>
+          <t>33790</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49515</t>
+          <t>22806</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>81833</t>
+          <t>47847</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7788</t>
+          <t>7819</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25756</t>
+          <t>25908</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7306</t>
+          <t>7653</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21784</t>
+          <t>22413</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>18297</t>
+          <t>18981</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>43345</t>
+          <t>43395</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4241,112 +4241,112 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Pan, tostadas, galletas, cereales, bolleria, ...</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>722</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24706</t>
+          <t>774630</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14948</t>
+          <t>746821</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36865</t>
+          <t>799108</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9084</t>
+          <t>1133501</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4075</t>
+          <t>1106634</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17528</t>
+          <t>1158655</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1775</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>33790</t>
+          <t>1908131</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>22274</t>
+          <t>1865731</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>48222</t>
+          <t>1943881</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>84,21%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1757236</t>
+          <t>1750540</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1810917</t>
+          <t>1808533</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1581981</t>
+          <t>1581076</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1629233</t>
+          <t>1630485</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3354901</t>
+          <t>3356886</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3426260</t>
+          <t>3429233</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,28%</t>
         </is>
       </c>
     </row>
@@ -4471,112 +4471,112 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Pan, tostadas, galletas, cereales, bolleria, ...</t>
+          <t>Fruta y/o zumo</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1487</t>
+          <t>226</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1573033</t>
+          <t>240805</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1535675</t>
+          <t>211815</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1606535</t>
+          <t>271700</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>211</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1435794</t>
+          <t>227367</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1403433</t>
+          <t>198846</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1469456</t>
+          <t>260126</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>2816</t>
+          <t>437</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>3008827</t>
+          <t>468173</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2954366</t>
+          <t>427332</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3055533</t>
+          <t>506085</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>13,62%</t>
         </is>
       </c>
     </row>
@@ -4584,112 +4584,112 @@
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Fruta y/o zumo</t>
+          <t>Alimentos como huevos, queso, jamón, ...</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>240805</t>
+          <t>92400</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>214691</t>
+          <t>74826</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>274428</t>
+          <t>112012</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>227367</t>
+          <t>50201</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>202418</t>
+          <t>35586</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>257895</t>
+          <t>66396</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>137</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>468173</t>
+          <t>142601</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>429018</t>
+          <t>120018</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>514987</t>
+          <t>164970</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -4697,112 +4697,112 @@
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Alimentos como huevos, queso, jamón, ...</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>92400</t>
+          <t>52560</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75518</t>
+          <t>37385</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>113114</t>
+          <t>70123</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>50201</t>
+          <t>50315</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36207</t>
+          <t>35681</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65353</t>
+          <t>65772</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>91</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>142601</t>
+          <t>102875</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>120946</t>
+          <t>84475</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>168304</t>
+          <t>127995</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11277</t>
+          <t>11092</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29574</t>
+          <t>28822</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,47 +4840,47 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>16922</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>10091</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>26774</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
           <t>0,58%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>16922</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>9821</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>27237</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>25079</t>
+          <t>24238</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>49865</t>
+          <t>49735</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,7 +4910,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4923,112 +4923,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Pan, tostadas, galletas, cereales, bolleria, ...</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>1487</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>52560</t>
+          <t>1573033</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>38862</t>
+          <t>1531622</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>69422</t>
+          <t>1609705</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>50315</t>
+          <t>1435794</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>36495</t>
+          <t>1400113</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>65413</t>
+          <t>1465067</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>102875</t>
+          <t>3008827</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>82507</t>
+          <t>2960607</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>127730</t>
+          <t>3054696</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>82,2%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>424972</t>
+          <t>426190</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>451810</t>
+          <t>451697</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>427268</t>
+          <t>427606</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>445050</t>
+          <t>445066</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>860766</t>
+          <t>859939</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>891235</t>
+          <t>890880</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,02%</t>
         </is>
       </c>
     </row>
@@ -5153,112 +5153,112 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Pan, tostadas, galletas, cereales, bolleria, ...</t>
+          <t>Fruta y/o zumo</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>389343</t>
+          <t>82815</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>371502</t>
+          <t>66508</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>408008</t>
+          <t>102675</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>73</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>373721</t>
+          <t>84882</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>354465</t>
+          <t>67402</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>390172</t>
+          <t>104484</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>149</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>763064</t>
+          <t>167697</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>734269</t>
+          <t>145049</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>784306</t>
+          <t>194569</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>20,75%</t>
         </is>
       </c>
     </row>
@@ -5266,112 +5266,112 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Fruta y/o zumo</t>
+          <t>Alimentos como huevos, queso, jamón, ...</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>82815</t>
+          <t>12149</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>67807</t>
+          <t>6100</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>102571</t>
+          <t>21395</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>84882</t>
+          <t>7080</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>69460</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>103350</t>
+          <t>15660</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>167697</t>
+          <t>19229</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>142551</t>
+          <t>12096</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>193914</t>
+          <t>30699</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -5379,112 +5379,112 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Alimentos como huevos, queso, jamón, ...</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12149</t>
+          <t>10775</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7009</t>
+          <t>4896</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21432</t>
+          <t>19964</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7080</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2808</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14618</t>
+          <t>6911</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>19229</t>
+          <t>12745</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10967</t>
+          <t>6636</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>29646</t>
+          <t>22782</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>937</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8893</t>
+          <t>7901</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4092</t>
+          <t>4688</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18485</t>
+          <t>19253</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>22090</t>
+          <t>23315</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -5605,112 +5605,112 @@
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Pan, tostadas, galletas, cereales, bolleria, ...</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>355</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10775</t>
+          <t>389343</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>369534</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21207</t>
+          <t>405715</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>337</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1970</t>
+          <t>373721</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>353562</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6284</t>
+          <t>389612</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>692</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>12745</t>
+          <t>763064</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6706</t>
+          <t>737248</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>22977</t>
+          <t>789171</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>84,17%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3084153</t>
+          <t>3085992</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3154136</t>
+          <t>3156079</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3285065</t>
+          <t>3283910</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3348488</t>
+          <t>3350093</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6395451</t>
+          <t>6397560</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6490695</t>
+          <t>6493679</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,27%</t>
         </is>
       </c>
     </row>
@@ -5835,112 +5835,112 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Pan, tostadas, galletas, cereales, bolleria, ...</t>
+          <t>Fruta y/o zumo</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2564</t>
+          <t>381</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2737006</t>
+          <t>410555</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2686844</t>
+          <t>372430</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2782882</t>
+          <t>452990</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2719</t>
+          <t>408</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2943017</t>
+          <t>445465</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2896717</t>
+          <t>407098</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2988904</t>
+          <t>488123</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>5283</t>
+          <t>789</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5680021</t>
+          <t>856020</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5612155</t>
+          <t>801499</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5746297</t>
+          <t>916580</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>13,17%</t>
         </is>
       </c>
     </row>
@@ -5948,112 +5948,112 @@
       <c r="A24" s="1" t="n"/>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Fruta y/o zumo</t>
+          <t>Alimentos como huevos, queso, jamón, ...</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>141</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>410555</t>
+          <t>143221</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>372518</t>
+          <t>122919</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>451506</t>
+          <t>171044</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>74</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>445465</t>
+          <t>82684</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>409789</t>
+          <t>63798</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>486565</t>
+          <t>102506</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>215</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>856020</t>
+          <t>225905</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>796988</t>
+          <t>197555</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>914276</t>
+          <t>260064</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -6061,112 +6061,112 @@
       <c r="A25" s="1" t="n"/>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Alimentos como huevos, queso, jamón, ...</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>76</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>143221</t>
+          <t>88041</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>120220</t>
+          <t>69274</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>167324</t>
+          <t>111172</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>82684</t>
+          <t>61369</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>63711</t>
+          <t>47537</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>102171</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>132</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>225905</t>
+          <t>149410</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>197586</t>
+          <t>125832</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>258156</t>
+          <t>176501</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>24072</t>
+          <t>24543</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>50936</t>
+          <t>50512</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>28599</t>
+          <t>29393</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>54699</t>
+          <t>55694</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>59501</t>
+          <t>59932</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>96166</t>
+          <t>95883</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,7 +6274,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6287,112 +6287,112 @@
       <c r="A27" s="1" t="n"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Pan, tostadas, galletas, cereales, bolleria, ...</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>88041</t>
+          <t>2737006</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>70241</t>
+          <t>2684846</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>111872</t>
+          <t>2783083</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>61369</t>
+          <t>2943017</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>47358</t>
+          <t>2890144</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>78880</t>
+          <t>2984308</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>5283</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>149410</t>
+          <t>5680021</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>126026</t>
+          <t>5612448</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>177936</t>
+          <t>5752035</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>82,62%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según alimentos que desayuna habitualmente (multirrespuesta) en 2016</t>
+          <t>Población según alimentos que desayuna habitualmente (multirrespuesta) en 2016 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>670733</t>
+          <t>670548</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>702549</t>
+          <t>701934</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>939954</t>
+          <t>938833</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>965836</t>
+          <t>965222</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1622654</t>
+          <t>1622079</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1661284</t>
+          <t>1659425</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,04%</t>
         </is>
       </c>
     </row>
@@ -6748,112 +6748,112 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Pan, tostadas, galletas, cereales, bolleria, ...</t>
+          <t>Fruta y/o zumo</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>629319</t>
+          <t>61269</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>607792</t>
+          <t>47974</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>648870</t>
+          <t>77978</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>878631</t>
+          <t>90218</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>856341</t>
+          <t>71584</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>898190</t>
+          <t>109037</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>1424</t>
+          <t>146</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1507950</t>
+          <t>151487</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1479065</t>
+          <t>130202</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1537562</t>
+          <t>179689</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -6861,112 +6861,112 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Fruta y/o zumo</t>
+          <t>Alimentos como huevos, queso, jamón, ...</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>61269</t>
+          <t>27669</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>49384</t>
+          <t>17992</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>78449</t>
+          <t>38622</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>90218</t>
+          <t>41069</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>72732</t>
+          <t>29183</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>110824</t>
+          <t>55797</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>64</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>151487</t>
+          <t>68738</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>129351</t>
+          <t>54129</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>176645</t>
+          <t>86870</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -6974,112 +6974,112 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Alimentos como huevos, queso, jamón, ...</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27669</t>
+          <t>11023</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18547</t>
+          <t>5522</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37855</t>
+          <t>19830</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>41069</t>
+          <t>5783</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30001</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56480</t>
+          <t>11647</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>68738</t>
+          <t>16806</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>54238</t>
+          <t>9951</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>87473</t>
+          <t>26430</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17792</t>
+          <t>17942</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36626</t>
+          <t>36924</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>30742</t>
+          <t>30691</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>57306</t>
+          <t>56787</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>54396</t>
+          <t>54678</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>85063</t>
+          <t>87744</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -7200,112 +7200,112 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Pan, tostadas, galletas, cereales, bolleria, ...</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>640</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11023</t>
+          <t>629319</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>607798</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20365</t>
+          <t>646790</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>784</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5783</t>
+          <t>878631</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>854966</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12064</t>
+          <t>896833</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1424</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>16806</t>
+          <t>1507950</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>9635</t>
+          <t>1477667</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>26463</t>
+          <t>1536166</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>87,98%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1832143</t>
+          <t>1835592</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1890578</t>
+          <t>1890382</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1817615</t>
+          <t>1813551</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1864567</t>
+          <t>1861511</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3662714</t>
+          <t>3665605</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3734823</t>
+          <t>3738188</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>92,06%</t>
         </is>
       </c>
     </row>
@@ -7430,112 +7430,112 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Pan, tostadas, galletas, cereales, bolleria, ...</t>
+          <t>Fruta y/o zumo</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>265</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1733555</t>
+          <t>287985</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1696369</t>
+          <t>256870</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1763237</t>
+          <t>317722</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1643</t>
+          <t>273</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1715734</t>
+          <t>282987</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1684891</t>
+          <t>253496</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1744963</t>
+          <t>314966</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>3276</t>
+          <t>538</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>3449289</t>
+          <t>570972</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3401850</t>
+          <t>530041</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3494385</t>
+          <t>616319</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>15,18%</t>
         </is>
       </c>
     </row>
@@ -7543,112 +7543,112 @@
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Fruta y/o zumo</t>
+          <t>Alimentos como huevos, queso, jamón, ...</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>164</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>287985</t>
+          <t>173035</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>257409</t>
+          <t>148018</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>319548</t>
+          <t>198268</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>130</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>282987</t>
+          <t>136243</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>251140</t>
+          <t>112940</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>317015</t>
+          <t>160244</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>294</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>570972</t>
+          <t>309277</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>526835</t>
+          <t>274563</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>619239</t>
+          <t>344045</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -7656,112 +7656,112 @@
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Alimentos como huevos, queso, jamón, ...</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>173035</t>
+          <t>47813</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>148713</t>
+          <t>35541</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>198247</t>
+          <t>64209</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>136243</t>
+          <t>28501</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>115453</t>
+          <t>19545</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>160555</t>
+          <t>40294</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>71</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>309277</t>
+          <t>76314</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>275421</t>
+          <t>60920</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>345051</t>
+          <t>95397</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>67020</t>
+          <t>65898</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>102542</t>
+          <t>103937</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>60025</t>
+          <t>56964</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>92119</t>
+          <t>91687</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>133164</t>
+          <t>132615</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>185463</t>
+          <t>184343</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -7882,112 +7882,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Pan, tostadas, galletas, cereales, bolleria, ...</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>1633</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>47813</t>
+          <t>1733555</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>34319</t>
+          <t>1700920</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>64446</t>
+          <t>1765240</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>1643</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28501</t>
+          <t>1715734</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19329</t>
+          <t>1684685</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>40428</t>
+          <t>1744789</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>76314</t>
+          <t>3449289</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>59346</t>
+          <t>3405379</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>94291</t>
+          <t>3499399</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>86,18%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>500293</t>
+          <t>500073</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>523709</t>
+          <t>523686</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,7 +8029,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>497893</t>
+          <t>495742</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>520947</t>
+          <t>519599</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1003316</t>
+          <t>1004856</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1038504</t>
+          <t>1039863</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,88%</t>
         </is>
       </c>
     </row>
@@ -8112,112 +8112,112 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Pan, tostadas, galletas, cereales, bolleria, ...</t>
+          <t>Fruta y/o zumo</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>486015</t>
+          <t>88169</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>470352</t>
+          <t>72083</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>501611</t>
+          <t>108917</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>476</t>
+          <t>93</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>499108</t>
+          <t>96292</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>485006</t>
+          <t>78722</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>511372</t>
+          <t>114762</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>174</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>985124</t>
+          <t>184461</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>965137</t>
+          <t>160253</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1006313</t>
+          <t>211878</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>19,33%</t>
         </is>
       </c>
     </row>
@@ -8225,112 +8225,112 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Fruta y/o zumo</t>
+          <t>Alimentos como huevos, queso, jamón, ...</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>44</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>88169</t>
+          <t>48155</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>70903</t>
+          <t>36572</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>107268</t>
+          <t>62013</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>96292</t>
+          <t>33067</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>78215</t>
+          <t>23044</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>114864</t>
+          <t>45853</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>75</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>184461</t>
+          <t>81221</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>160711</t>
+          <t>65267</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>212816</t>
+          <t>103895</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -8338,112 +8338,112 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Alimentos como huevos, queso, jamón, ...</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>48155</t>
+          <t>5542</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>35678</t>
+          <t>1912</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>64060</t>
+          <t>13108</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>33067</t>
+          <t>948</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22223</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46479</t>
+          <t>5114</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>81221</t>
+          <t>6490</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>63836</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>100278</t>
+          <t>13105</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>16424</t>
+          <t>18266</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>37163</t>
+          <t>41719</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20997</t>
+          <t>20664</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>45536</t>
+          <t>43159</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>44484</t>
+          <t>44196</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>75391</t>
+          <t>75998</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -8564,112 +8564,112 @@
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Pan, tostadas, galletas, cereales, bolleria, ...</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>447</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5542</t>
+          <t>486015</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1978</t>
+          <t>468458</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13246</t>
+          <t>501021</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>476</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>499108</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>485644</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4756</t>
+          <t>511463</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>923</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>6490</t>
+          <t>985124</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2798</t>
+          <t>963252</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>14204</t>
+          <t>1003649</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>91,57%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3028317</t>
+          <t>3024808</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3097145</t>
+          <t>3095560</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3274397</t>
+          <t>3273370</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3329634</t>
+          <t>3329756</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6324201</t>
+          <t>6321457</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6412535</t>
+          <t>6413685</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,92%</t>
         </is>
       </c>
     </row>
@@ -8794,112 +8794,112 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Pan, tostadas, galletas, cereales, bolleria, ...</t>
+          <t>Fruta y/o zumo</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2720</t>
+          <t>409</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2848889</t>
+          <t>437423</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2804402</t>
+          <t>399092</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2894620</t>
+          <t>477614</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2903</t>
+          <t>449</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3093474</t>
+          <t>469497</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3054356</t>
+          <t>427892</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3134124</t>
+          <t>508433</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>5623</t>
+          <t>858</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5942364</t>
+          <t>906920</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5883234</t>
+          <t>852422</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6008745</t>
+          <t>965569</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -8907,112 +8907,112 @@
       <c r="A24" s="1" t="n"/>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Fruta y/o zumo</t>
+          <t>Alimentos como huevos, queso, jamón, ...</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>236</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>437423</t>
+          <t>248858</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>397952</t>
+          <t>217610</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>477383</t>
+          <t>279609</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>197</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>469497</t>
+          <t>210378</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>429618</t>
+          <t>183019</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>510955</t>
+          <t>240734</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>433</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>906920</t>
+          <t>459236</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>852752</t>
+          <t>418108</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>967373</t>
+          <t>500077</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -9020,112 +9020,112 @@
       <c r="A25" s="1" t="n"/>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Alimentos como huevos, queso, jamón, ...</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>58</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>248858</t>
+          <t>64378</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>220483</t>
+          <t>48676</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>282535</t>
+          <t>83476</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>210378</t>
+          <t>35232</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>181178</t>
+          <t>25397</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>242005</t>
+          <t>48899</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>93</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>459236</t>
+          <t>99610</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>419140</t>
+          <t>79524</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>503117</t>
+          <t>121193</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>115053</t>
+          <t>115908</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>164429</t>
+          <t>166439</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>123917</t>
+          <t>124290</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>172781</t>
+          <t>172905</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,7 +9198,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>253154</t>
+          <t>251454</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>317761</t>
+          <t>321853</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -9246,112 +9246,112 @@
       <c r="A27" s="1" t="n"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Pan, tostadas, galletas, cereales, bolleria, ...</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>2720</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>64378</t>
+          <t>2848889</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>48894</t>
+          <t>2800053</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>82576</t>
+          <t>2887800</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>2903</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>35232</t>
+          <t>3093474</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>25414</t>
+          <t>3051247</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>48927</t>
+          <t>3131138</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>5623</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>99610</t>
+          <t>5942364</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>80045</t>
+          <t>5881285</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>122383</t>
+          <t>5998855</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>86,91%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36$cafe-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36$cafe-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>937117</t>
+          <t>937761</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>969262</t>
+          <t>970124</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1208892</t>
+          <t>1213710</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1245283</t>
+          <t>1247195</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2159286</t>
+          <t>2159800</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2207589</t>
+          <t>2208767</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,36%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49788</t>
+          <t>47928</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>81110</t>
+          <t>80102</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>74834</t>
+          <t>74782</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>110494</t>
+          <t>112317</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>132649</t>
+          <t>133657</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>181229</t>
+          <t>181708</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,76%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13584</t>
+          <t>13902</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33651</t>
+          <t>33576</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9354</t>
+          <t>9026</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25058</t>
+          <t>24803</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>26587</t>
+          <t>27388</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>51993</t>
+          <t>54849</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17703</t>
+          <t>17604</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39289</t>
+          <t>38002</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8768</t>
+          <t>8615</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25200</t>
+          <t>24377</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30247</t>
+          <t>30678</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55864</t>
+          <t>56287</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19378</t>
+          <t>19646</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>40175</t>
+          <t>40154</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>21690</t>
+          <t>20871</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>43271</t>
+          <t>42049</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>46292</t>
+          <t>46753</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>77242</t>
+          <t>75626</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>756456</t>
+          <t>757203</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>813061</t>
+          <t>810832</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1312,12 +1312,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1021960</t>
+          <t>1023393</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1079089</t>
+          <t>1081028</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1367,12 +1367,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1794491</t>
+          <t>1799920</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1875983</t>
+          <t>1875900</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1513540</t>
+          <t>1514446</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1563711</t>
+          <t>1563602</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1401031</t>
+          <t>1400984</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1447547</t>
+          <t>1447157</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2928143</t>
+          <t>2929578</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2996431</t>
+          <t>2995219</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,37%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>112230</t>
+          <t>110361</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>158636</t>
+          <t>157353</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>169040</t>
+          <t>167220</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>220069</t>
+          <t>219398</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>291855</t>
+          <t>291450</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>360430</t>
+          <t>360689</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>61341</t>
+          <t>61046</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>97172</t>
+          <t>97112</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>35112</t>
+          <t>34341</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62535</t>
+          <t>62829</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>102310</t>
+          <t>103543</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>148443</t>
+          <t>149600</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23731</t>
+          <t>24060</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45124</t>
+          <t>46346</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21118</t>
+          <t>21146</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42055</t>
+          <t>41919</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50228</t>
+          <t>50540</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>81451</t>
+          <t>81573</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15003</t>
+          <t>15403</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35505</t>
+          <t>36410</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13287</t>
+          <t>13673</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31598</t>
+          <t>31719</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>33038</t>
+          <t>32583</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>60997</t>
+          <t>58912</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1260857</t>
+          <t>1263315</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1331896</t>
+          <t>1330622</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1196006</t>
+          <t>1197212</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1262123</t>
+          <t>1262256</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2476859</t>
+          <t>2475695</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2576084</t>
+          <t>2574326</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>78,53%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>483607</t>
+          <t>481936</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>510235</t>
+          <t>510517</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>421618</t>
+          <t>422203</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>446049</t>
+          <t>447985</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>913680</t>
+          <t>913383</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>951878</t>
+          <t>951383</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,72%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>54085</t>
+          <t>53918</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>88940</t>
+          <t>87111</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>58777</t>
+          <t>59406</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>90631</t>
+          <t>92870</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>121458</t>
+          <t>118649</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>165267</t>
+          <t>165441</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,12%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10652</t>
+          <t>10347</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27958</t>
+          <t>28754</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3560</t>
+          <t>3319</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16974</t>
+          <t>15876</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>16812</t>
+          <t>16825</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>38790</t>
+          <t>39086</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2819</t>
+          <t>2799</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13931</t>
+          <t>14003</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3418</t>
+          <t>3425</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15343</t>
+          <t>16460</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8656</t>
+          <t>8414</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24431</t>
+          <t>24625</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2630</t>
+          <t>3163</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13329</t>
+          <t>14011</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>971</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9038</t>
+          <t>9539</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5179</t>
+          <t>5203</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19134</t>
+          <t>18948</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -2661,12 +2661,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>396327</t>
+          <t>394556</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>436775</t>
+          <t>437186</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>337044</t>
+          <t>336468</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>374473</t>
+          <t>375331</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2731,12 +2731,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>740772</t>
+          <t>743451</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>799019</t>
+          <t>802758</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2746,12 +2746,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>78,24%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2953472</t>
+          <t>2958997</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3020686</t>
+          <t>3023394</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3055452</t>
+          <t>3056925</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3122071</t>
+          <t>3121659</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6033195</t>
+          <t>6039299</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6125749</t>
+          <t>6126045</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>232577</t>
+          <t>232687</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>300228</t>
+          <t>298110</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>321891</t>
+          <t>327110</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>392999</t>
+          <t>401198</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>573255</t>
+          <t>575757</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>671909</t>
+          <t>672395</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>96616</t>
+          <t>96059</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>143034</t>
+          <t>140992</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>55733</t>
+          <t>55299</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>89664</t>
+          <t>88606</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>161452</t>
+          <t>162356</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>216795</t>
+          <t>215852</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>52059</t>
+          <t>52434</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>85648</t>
+          <t>84976</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,47 +3132,47 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>53550</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>41150</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>72259</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
           <t>1,59%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>53550</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>39420</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>69792</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>101491</t>
+          <t>101631</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>145377</t>
+          <t>144151</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>46331</t>
+          <t>44323</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>77733</t>
+          <t>76151</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>42427</t>
+          <t>42586</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>71113</t>
+          <t>71838</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>93955</t>
+          <t>93219</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>138486</t>
+          <t>136291</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -3343,12 +3343,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2447433</t>
+          <t>2451542</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2549606</t>
+          <t>2544753</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3358,12 +3358,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2586715</t>
+          <t>2589879</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2685599</t>
+          <t>2683530</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>5069578</t>
+          <t>5064353</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>5206523</t>
+          <t>5203467</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>78,31%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>882054</t>
+          <t>879498</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>915238</t>
+          <t>913813</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1256719</t>
+          <t>1258033</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1288499</t>
+          <t>1288402</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2148660</t>
+          <t>2148884</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2195213</t>
+          <t>2197783</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,21%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>67951</t>
+          <t>69487</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>105299</t>
+          <t>107165</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>113525</t>
+          <t>112412</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>157483</t>
+          <t>156932</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>189979</t>
+          <t>193295</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>249970</t>
+          <t>249719</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,82%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28406</t>
+          <t>28041</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53026</t>
+          <t>52353</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16444</t>
+          <t>16169</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37288</t>
+          <t>37569</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>50186</t>
+          <t>48976</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>82481</t>
+          <t>80614</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15741</t>
+          <t>16469</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37699</t>
+          <t>38209</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3892</t>
+          <t>4151</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16968</t>
+          <t>17366</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22806</t>
+          <t>23326</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>47847</t>
+          <t>47780</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7819</t>
+          <t>7849</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25908</t>
+          <t>26362</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7653</t>
+          <t>7441</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22413</t>
+          <t>22175</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>18981</t>
+          <t>18163</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>43395</t>
+          <t>41432</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -4256,12 +4256,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>746821</t>
+          <t>747528</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>799108</t>
+          <t>797803</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4271,12 +4271,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4291,12 +4291,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1106634</t>
+          <t>1106383</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1158655</t>
+          <t>1158505</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1865731</t>
+          <t>1870066</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1943881</t>
+          <t>1944335</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,23%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1750540</t>
+          <t>1755552</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1808533</t>
+          <t>1810047</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1581076</t>
+          <t>1583595</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1630485</t>
+          <t>1630948</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3356886</t>
+          <t>3353180</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3429233</t>
+          <t>3426093</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,2%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>211815</t>
+          <t>213300</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>271700</t>
+          <t>270220</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>198846</t>
+          <t>201431</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>260126</t>
+          <t>260338</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>427332</t>
+          <t>425576</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>506085</t>
+          <t>511518</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,77%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>74826</t>
+          <t>75263</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>112012</t>
+          <t>112070</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>35586</t>
+          <t>37294</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>66396</t>
+          <t>67426</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>120018</t>
+          <t>121426</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>164970</t>
+          <t>168292</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37385</t>
+          <t>37609</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>70123</t>
+          <t>71976</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35681</t>
+          <t>36898</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65772</t>
+          <t>66325</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>84475</t>
+          <t>82627</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>127995</t>
+          <t>126269</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11092</t>
+          <t>11174</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28822</t>
+          <t>29517</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10091</t>
+          <t>10175</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26774</t>
+          <t>26378</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>24238</t>
+          <t>24488</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>49735</t>
+          <t>48199</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -4938,12 +4938,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1531622</t>
+          <t>1537025</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1609705</t>
+          <t>1609200</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4953,12 +4953,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4973,12 +4973,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1400113</t>
+          <t>1400044</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1465067</t>
+          <t>1466691</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4993,7 +4993,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5008,12 +5008,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2960607</t>
+          <t>2962296</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>3054696</t>
+          <t>3058476</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5023,12 +5023,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,31%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>426190</t>
+          <t>425129</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>451697</t>
+          <t>450493</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>427606</t>
+          <t>426937</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>445066</t>
+          <t>445730</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>859939</t>
+          <t>859929</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>890880</t>
+          <t>891261</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,06%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>66508</t>
+          <t>66433</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>102675</t>
+          <t>102068</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>67402</t>
+          <t>68234</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>104484</t>
+          <t>105588</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>143051</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>194569</t>
+          <t>195524</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,85%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6100</t>
+          <t>6696</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21395</t>
+          <t>20944</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15660</t>
+          <t>15504</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12096</t>
+          <t>11336</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>30699</t>
+          <t>29542</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4896</t>
+          <t>4971</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19964</t>
+          <t>21642</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6911</t>
+          <t>6013</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6636</t>
+          <t>6768</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22782</t>
+          <t>24535</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>945</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7901</t>
+          <t>7918</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4688</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19253</t>
+          <t>19675</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6640</t>
+          <t>6808</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>23315</t>
+          <t>22715</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -5620,12 +5620,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>369534</t>
+          <t>369310</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>405715</t>
+          <t>405357</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5635,12 +5635,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>353562</t>
+          <t>354776</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>389612</t>
+          <t>390449</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>737248</t>
+          <t>737190</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>789171</t>
+          <t>789354</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>84,19%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3085992</t>
+          <t>3085073</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3156079</t>
+          <t>3156255</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3283910</t>
+          <t>3291265</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3350093</t>
+          <t>3348060</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6397560</t>
+          <t>6395189</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6493679</t>
+          <t>6488198</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,19%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>372430</t>
+          <t>370014</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>452990</t>
+          <t>451923</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>407098</t>
+          <t>407256</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>488123</t>
+          <t>487599</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>801499</t>
+          <t>798985</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>916580</t>
+          <t>908902</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,06%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>122919</t>
+          <t>122375</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>171044</t>
+          <t>170026</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>63798</t>
+          <t>65160</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>102506</t>
+          <t>102486</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>197555</t>
+          <t>195871</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>260064</t>
+          <t>257529</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>69274</t>
+          <t>69255</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>111172</t>
+          <t>112381</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>47537</t>
+          <t>46621</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>80517</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>125832</t>
+          <t>126014</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>176501</t>
+          <t>177581</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>24543</t>
+          <t>24823</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>50512</t>
+          <t>50764</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>29393</t>
+          <t>27989</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>55694</t>
+          <t>56548</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>59932</t>
+          <t>59006</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>95883</t>
+          <t>94970</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -6302,12 +6302,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2684846</t>
+          <t>2688812</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2783083</t>
+          <t>2786480</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6317,12 +6317,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6337,12 +6337,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2890144</t>
+          <t>2895694</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2984308</t>
+          <t>2992790</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6352,12 +6352,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6372,12 +6372,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>5612448</t>
+          <t>5613672</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>5752035</t>
+          <t>5747563</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6387,12 +6387,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,56%</t>
         </is>
       </c>
     </row>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>670548</t>
+          <t>672895</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>701934</t>
+          <t>702019</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>938833</t>
+          <t>940490</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>965222</t>
+          <t>964971</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1622079</t>
+          <t>1621603</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1659425</t>
+          <t>1661936</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,18%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47974</t>
+          <t>47211</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77978</t>
+          <t>76701</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>71584</t>
+          <t>74999</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>109037</t>
+          <t>112044</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>130202</t>
+          <t>127817</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>179689</t>
+          <t>177349</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,16%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17992</t>
+          <t>18545</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38622</t>
+          <t>39598</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29183</t>
+          <t>28200</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>55797</t>
+          <t>55139</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>54129</t>
+          <t>54292</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>86870</t>
+          <t>85578</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5522</t>
+          <t>5776</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19830</t>
+          <t>20681</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11647</t>
+          <t>12411</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9951</t>
+          <t>9892</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17942</t>
+          <t>17260</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36924</t>
+          <t>37476</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>30691</t>
+          <t>30967</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>56787</t>
+          <t>56449</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>54678</t>
+          <t>54464</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>87744</t>
+          <t>87262</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>607798</t>
+          <t>607774</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>646790</t>
+          <t>649633</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7235,7 +7235,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>854966</t>
+          <t>856487</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>896833</t>
+          <t>897245</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1477667</t>
+          <t>1475490</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1536166</t>
+          <t>1535656</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,95%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1835592</t>
+          <t>1830957</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1890382</t>
+          <t>1891514</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1813551</t>
+          <t>1816313</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1861511</t>
+          <t>1863340</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3665605</t>
+          <t>3665778</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3738188</t>
+          <t>3737352</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,04%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>256870</t>
+          <t>259121</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>317722</t>
+          <t>322969</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>253496</t>
+          <t>251901</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>314966</t>
+          <t>316190</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>530041</t>
+          <t>526097</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>616319</t>
+          <t>617655</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,21%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>148018</t>
+          <t>150031</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>198268</t>
+          <t>201010</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>112940</t>
+          <t>115421</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>160244</t>
+          <t>162588</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>274563</t>
+          <t>276384</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>344045</t>
+          <t>346482</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35541</t>
+          <t>34704</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64209</t>
+          <t>63807</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19545</t>
+          <t>19106</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40294</t>
+          <t>40273</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,7 +7721,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>60920</t>
+          <t>62818</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>95397</t>
+          <t>97636</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>65898</t>
+          <t>66380</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>103937</t>
+          <t>103074</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>56964</t>
+          <t>58643</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>91687</t>
+          <t>92250</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>132615</t>
+          <t>133714</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>184343</t>
+          <t>183966</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -7897,12 +7897,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1700920</t>
+          <t>1696463</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1765240</t>
+          <t>1766606</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7912,12 +7912,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7932,12 +7932,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1684685</t>
+          <t>1683851</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1744789</t>
+          <t>1740440</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7947,12 +7947,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7967,12 +7967,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3405379</t>
+          <t>3406721</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>3499399</t>
+          <t>3495747</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7982,12 +7982,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,09%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>500073</t>
+          <t>501059</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>523686</t>
+          <t>524019</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>495742</t>
+          <t>496196</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>519599</t>
+          <t>520192</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1004856</t>
+          <t>1004306</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1039863</t>
+          <t>1038263</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,73%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>72083</t>
+          <t>70203</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>108917</t>
+          <t>107005</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>78722</t>
+          <t>78277</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>114762</t>
+          <t>114412</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>160253</t>
+          <t>159600</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>211878</t>
+          <t>211541</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,3%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>36572</t>
+          <t>34930</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>62013</t>
+          <t>62143</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>23044</t>
+          <t>21930</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>45853</t>
+          <t>46170</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>65267</t>
+          <t>65476</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>103895</t>
+          <t>102189</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>1884</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13108</t>
+          <t>12137</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5114</t>
+          <t>6294</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>2789</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13105</t>
+          <t>13218</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18266</t>
+          <t>17606</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>41719</t>
+          <t>38917</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20664</t>
+          <t>20362</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43159</t>
+          <t>43695</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>44196</t>
+          <t>44198</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>75998</t>
+          <t>75492</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -8579,12 +8579,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>468458</t>
+          <t>469230</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>501021</t>
+          <t>499963</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8594,12 +8594,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8614,12 +8614,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>485644</t>
+          <t>484684</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>511463</t>
+          <t>510340</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8649,12 +8649,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>963252</t>
+          <t>964113</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1003649</t>
+          <t>1006214</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,81%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3024808</t>
+          <t>3030833</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3095560</t>
+          <t>3098287</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3273370</t>
+          <t>3274730</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3329756</t>
+          <t>3334357</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6321457</t>
+          <t>6323001</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6413685</t>
+          <t>6413524</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,7 +8781,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>399092</t>
+          <t>402405</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>477614</t>
+          <t>480831</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>427892</t>
+          <t>433555</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>508433</t>
+          <t>513658</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>852422</t>
+          <t>846830</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>965569</t>
+          <t>961595</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>217610</t>
+          <t>217447</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>279609</t>
+          <t>280190</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>183019</t>
+          <t>182461</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>240734</t>
+          <t>241569</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>418108</t>
+          <t>415938</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>500077</t>
+          <t>500066</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>48676</t>
+          <t>48955</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>83476</t>
+          <t>82000</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,77 +9050,77 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>35232</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>24729</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>48978</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>99610</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>80555</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>121522</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
           <t>1,44%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,47%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>35232</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>25397</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>48899</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>99610</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>79524</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>121193</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>115908</t>
+          <t>114794</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>166439</t>
+          <t>163325</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>124290</t>
+          <t>122497</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>172905</t>
+          <t>172226</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>251454</t>
+          <t>252346</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>321853</t>
+          <t>319397</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -9261,12 +9261,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2800053</t>
+          <t>2799118</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2887800</t>
+          <t>2887908</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -9296,12 +9296,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3051247</t>
+          <t>3055859</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3131138</t>
+          <t>3132720</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9331,12 +9331,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>5881285</t>
+          <t>5882007</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>5998855</t>
+          <t>6002129</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>86,96%</t>
         </is>
       </c>
     </row>
